--- a/data/trans_dic/BARTHEL_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/BARTHEL_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,47; 98,55</t>
+          <t>1,37; 14,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74,77; 100,0</t>
+          <t>0,0; 24,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,33; 98,89</t>
+          <t>1,12; 15,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90,88; 97,38</t>
+          <t>2,93; 9,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,64; 100,0</t>
+          <t>0,0; 24,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,85; 100,0</t>
+          <t>0,0; 26,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,14; 100,0</t>
+          <t>0,0; 21,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>86,07; 95,97</t>
+          <t>3,53; 13,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>86,8; 98,01</t>
+          <t>1,91; 12,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81,93; 98,36</t>
+          <t>1,57; 18,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87,35; 98,05</t>
+          <t>2,04; 11,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,75; 95,92</t>
+          <t>3,97; 9,44</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,07; 100,0</t>
+          <t>0,0; 6,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,67; 98,02</t>
+          <t>3,17; 21,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76,11; 94,27</t>
+          <t>6,52; 24,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87,53; 96,68</t>
+          <t>3,43; 13,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,61; 94,4</t>
+          <t>5,74; 46,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,68; 100,0</t>
+          <t>5,44; 38,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,4; 92,13</t>
+          <t>7,31; 60,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>77,94; 93,08</t>
+          <t>6,8; 20,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>85,86; 98,27</t>
+          <t>1,68; 14,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78,27; 95,67</t>
+          <t>4,4; 21,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,04; 91,06</t>
+          <t>9,21; 29,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86,36; 93,88</t>
+          <t>5,88; 13,79</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,7; 96,39</t>
+          <t>3,62; 16,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,34; 95,65</t>
+          <t>4,28; 15,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,11; 95,08</t>
+          <t>5,25; 14,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81,02; 91,49</t>
+          <t>8,7; 19,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,0; 95,27</t>
+          <t>4,72; 40,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,42; 88,36</t>
+          <t>11,48; 34,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,23; 92,76</t>
+          <t>5,69; 29,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70,3; 86,37</t>
+          <t>13,0; 28,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81,57; 94,34</t>
+          <t>6,01; 18,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81,09; 91,96</t>
+          <t>7,89; 19,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82,96; 92,89</t>
+          <t>7,02; 16,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>79,29; 88,55</t>
+          <t>11,8; 20,67</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,57; 94,29</t>
+          <t>5,73; 12,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,27; 84,79</t>
+          <t>15,21; 26,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,13; 92,89</t>
+          <t>6,7; 14,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78,21; 85,95</t>
+          <t>14,32; 22,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,31; 96,37</t>
+          <t>3,61; 15,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,14; 87,49</t>
+          <t>13,63; 34,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,43; 87,1</t>
+          <t>12,75; 32,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>81,74; 98,58</t>
+          <t>1,48; 18,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88,16; 94,01</t>
+          <t>6,07; 12,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73,36; 83,22</t>
+          <t>16,49; 26,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81,27; 89,81</t>
+          <t>9,83; 17,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,7; 95,69</t>
+          <t>4,29; 18,58</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,78; 93,5</t>
+          <t>6,54; 25,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>76,42; 90,84</t>
+          <t>9,22; 24,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74,21; 86,59</t>
+          <t>13,18; 26,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79,99; 90,7</t>
+          <t>9,68; 20,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,8; 88,76</t>
+          <t>11,86; 29,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,78; 72,79</t>
+          <t>27,23; 41,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,24; 83,67</t>
+          <t>15,97; 30,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>67,32; 75,36</t>
+          <t>24,52; 32,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>76,73; 88,68</t>
+          <t>10,93; 23,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67,29; 77,67</t>
+          <t>22,6; 33,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73,9; 83,76</t>
+          <t>16,43; 26,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,22; 79,26</t>
+          <t>20,75; 27,81</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1364,47 +1364,47 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,55; 100,0</t>
+          <t>0,0; 71,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83,44; 90,15</t>
+          <t>9,9; 16,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,55; 79,69</t>
+          <t>20,03; 29,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71,85; 81,18</t>
+          <t>18,88; 28,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69,77; 77,01</t>
+          <t>23,11; 30,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83,1; 90,13</t>
+          <t>9,46; 16,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70,94; 79,96</t>
+          <t>20,03; 28,44</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71,85; 81,18</t>
+          <t>18,88; 28,22</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69,69; 77,12</t>
+          <t>23,12; 30,15</t>
         </is>
       </c>
     </row>
@@ -1489,62 +1489,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,61; 94,13</t>
+          <t>5,94; 10,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>81,53; 88,33</t>
+          <t>11,66; 18,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85,61; 90,51</t>
+          <t>9,5; 14,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84,7; 89,02</t>
+          <t>11,11; 15,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,56; 89,03</t>
+          <t>10,84; 16,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,81; 77,47</t>
+          <t>22,67; 29,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,67; 81,15</t>
+          <t>18,69; 25,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>76,53; 90,28</t>
+          <t>9,26; 23,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>87,06; 90,73</t>
+          <t>9,5; 13,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76,51; 81,04</t>
+          <t>18,88; 23,78</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80,13; 84,64</t>
+          <t>15,44; 19,78</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,01; 89,13</t>
+          <t>9,97; 19,08</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1791,62 +1791,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
         </is>
       </c>
     </row>
@@ -1859,62 +1859,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>56561</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40682</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65465</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101562</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27539</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23137</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34301</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60389</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84100</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63819</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99767</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>161951</t>
+          <t>10949</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>51100; 58916</t>
+          <t>819; 8645</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32836; 43918</t>
+          <t>0; 10781</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59262; 67887</t>
+          <t>769; 10485</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97772; 104765</t>
+          <t>3153; 10406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23067; 29709</t>
+          <t>0; 7232</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18422; 25289</t>
+          <t>0; 6777</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28454; 36888</t>
+          <t>0; 8084</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56222; 62686</t>
+          <t>2303; 8723</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77676; 87716</t>
+          <t>1712; 11430</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56702; 68073</t>
+          <t>1088; 12892</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92188; 103479</t>
+          <t>2155; 12617</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>156914; 165852</t>
+          <t>6863; 16316</t>
         </is>
       </c>
     </row>
@@ -1999,62 +1999,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -2067,62 +2067,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>50011</t>
+          <t>819</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55080</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46106</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88151</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>12538</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12843</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40680</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>62550</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70659</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58949</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>128831</t>
+          <t>12750</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46292; 50830</t>
+          <t>0; 3501</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47089; 59430</t>
+          <t>1921; 13243</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40600; 50285</t>
+          <t>3476; 12984</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83147; 91848</t>
+          <t>3259; 12557</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8620; 14902</t>
+          <t>906; 7293</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11281; 18902</t>
+          <t>1029; 7360</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6753; 16205</t>
+          <t>1285; 10682</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36309; 43360</t>
+          <t>3167; 9754</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57195; 65465</t>
+          <t>1119; 9461</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62247; 76087</t>
+          <t>3503; 17229</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51097; 64588</t>
+          <t>6532; 20667</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>122266; 132921</t>
+          <t>8325; 19526</t>
         </is>
       </c>
     </row>
@@ -2207,62 +2207,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -2275,62 +2275,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65637</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>108335</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>109017</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88588</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19802</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43035</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42201</t>
+          <t>10588</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>85440</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151370</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147958</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>130789</t>
+          <t>24069</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>60058; 69160</t>
+          <t>2599; 11865</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98884; 113495</t>
+          <t>5073; 18822</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102359; 114348</t>
+          <t>6317; 17773</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82699; 93381</t>
+          <t>8881; 19929</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14564; 23126</t>
+          <t>1146; 9818</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35727; 48260</t>
+          <t>6269; 19079</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31989; 42863</t>
+          <t>2627; 13510</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37109; 45594</t>
+          <t>6864; 15201</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78336; 90597</t>
+          <t>5768; 18219</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>140497; 159338</t>
+          <t>13663; 32938</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138104; 154639</t>
+          <t>11692; 27728</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>122781; 137129</t>
+          <t>18278; 32007</t>
         </is>
       </c>
     </row>
@@ -2415,62 +2415,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>111</t>
         </is>
       </c>
     </row>
@@ -2483,62 +2483,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>237670</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>183254</t>
+          <t>48499</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>182852</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194087</t>
+          <t>42252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78398</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46111</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78286</t>
+          <t>20760</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>305799</t>
+          <t>20344</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>316068</t>
+          <t>29756</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>229365</t>
+          <t>62483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>261138</t>
+          <t>41764</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>499885</t>
+          <t>62596</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>227736; 245210</t>
+          <t>14908; 32456</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>169806; 196513</t>
+          <t>35259; 62267</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>173544; 189368</t>
+          <t>13660; 29804</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>184829; 203142</t>
+          <t>33837; 52175</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>72297; 82641</t>
+          <t>3091; 13405</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39146; 52575</t>
+          <t>8190; 20763</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68765; 86274</t>
+          <t>12631; 32014</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>266590; 321513</t>
+          <t>4826; 59499</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304862; 325103</t>
+          <t>20998; 42468</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>214110; 242889</t>
+          <t>48119; 78742</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>246175; 272031</t>
+          <t>29781; 54220</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>459539; 538259</t>
+          <t>24143; 104488</t>
         </is>
       </c>
     </row>
@@ -2623,62 +2623,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>74</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>59</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>155</t>
         </is>
       </c>
     </row>
@@ -2691,62 +2691,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>48125</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86764</t>
+          <t>15932</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117790</t>
+          <t>27431</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78881</t>
+          <t>13125</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>77802</t>
+          <t>18448</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>124312</t>
+          <t>64088</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>123522</t>
+          <t>36028</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>145163</t>
+          <t>58103</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>125927</t>
+          <t>25788</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211076</t>
+          <t>80020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>241313</t>
+          <t>63458</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>224044</t>
+          <t>71228</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>42032; 51862</t>
+          <t>3625; 14334</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78481; 93293</t>
+          <t>9467; 24772</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107773; 125744</t>
+          <t>19141; 38179</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73592; 83446</t>
+          <t>8908; 18986</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>69106; 85434</t>
+          <t>11415; 28647</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>110748; 137137</t>
+          <t>51296; 77971</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>112065; 133502</t>
+          <t>25484; 48693</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>136839; 153186</t>
+          <t>49845; 66374</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>116405; 134534</t>
+          <t>16586; 35522</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>195883; 226107</t>
+          <t>65797; 96909</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>225219; 255290</t>
+          <t>50078; 79596</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>213244; 234032</t>
+          <t>61275; 82117</t>
         </is>
       </c>
     </row>
@@ -2831,62 +2831,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>162</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>87</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>77</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>164</t>
         </is>
       </c>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2914,47 +2914,47 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>369668</t>
+          <t>55402</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>298350</t>
+          <t>96354</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>315722</t>
+          <t>97361</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>234682</t>
+          <t>84354</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>373313</t>
+          <t>55402</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>300338</t>
+          <t>96354</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>315722</t>
+          <t>97361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>236794</t>
+          <t>85446</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2324; 3645</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>856; 1988</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>530; 3204</t>
+          <t>0; 2275</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>354663; 383202</t>
+          <t>42085; 69927</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>278480; 314523</t>
+          <t>79062; 114756</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>296794; 335356</t>
+          <t>77971; 116582</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>222586; 245687</t>
+          <t>73745; 96987</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>356271; 386397</t>
+          <t>40545; 71356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>281427; 317188</t>
+          <t>79475; 112808</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>296794; 335356</t>
+          <t>77971; 116582</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>224577; 248501</t>
+          <t>74514; 97153</t>
         </is>
       </c>
     </row>
@@ -3039,62 +3039,62 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>133</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>379</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>126</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>247</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>515</t>
         </is>
       </c>
     </row>
@@ -3107,62 +3107,62 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>461650</t>
+          <t>39901</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>476102</t>
+          <t>83535</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>521230</t>
+          <t>70098</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>553380</t>
+          <t>82814</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>585747</t>
+          <t>91095</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>550525</t>
+          <t>191480</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>603615</t>
+          <t>168749</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>828914</t>
+          <t>184224</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1047397</t>
+          <t>130996</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1026627</t>
+          <t>275015</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1124845</t>
+          <t>238847</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1382295</t>
+          <t>267038</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>449431; 472109</t>
+          <t>29768; 52277</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>456251; 494339</t>
+          <t>65275; 101241</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>506213; 535239</t>
+          <t>56165; 86052</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>538827; 566322</t>
+          <t>70676; 96669</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>565581; 602613</t>
+          <t>73382; 109071</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>525393; 574822</t>
+          <t>168229; 215483</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>576703; 626786</t>
+          <t>144350; 195689</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>775362; 914622</t>
+          <t>93815; 237972</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1025888; 1069161</t>
+          <t>111958; 155046</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>995930; 1054910</t>
+          <t>245762; 309472</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1092790; 1154209</t>
+          <t>210555; 269768</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1336137; 1470055</t>
+          <t>164455; 314725</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/BARTHEL_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/BARTHEL_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 14,46</t>
+          <t>1,33; 14,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,55</t>
+          <t>0,0; 24,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 15,27</t>
+          <t>1,09; 13,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 9,67</t>
+          <t>2,53; 8,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,34</t>
+          <t>0,0; 22,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,8</t>
+          <t>0,0; 26,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,91</t>
+          <t>0,0; 23,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 13,35</t>
+          <t>3,52; 13,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 12,77</t>
+          <t>2,15; 13,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 18,63</t>
+          <t>1,62; 19,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 11,96</t>
+          <t>1,89; 12,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 9,44</t>
+          <t>3,83; 8,98</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,89</t>
+          <t>0,0; 9,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 21,84</t>
+          <t>2,05; 23,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,52; 24,34</t>
+          <t>6,56; 24,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 13,22</t>
+          <t>3,43; 12,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 46,2</t>
+          <t>5,75; 48,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 38,94</t>
+          <t>5,32; 42,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 60,74</t>
+          <t>7,63; 57,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 20,94</t>
+          <t>6,77; 20,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 14,2</t>
+          <t>1,77; 13,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 21,66</t>
+          <t>5,21; 22,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,21; 29,14</t>
+          <t>9,04; 28,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,88; 13,79</t>
+          <t>5,81; 13,56</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 16,54</t>
+          <t>3,64; 16,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 15,86</t>
+          <t>4,42; 16,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 14,78</t>
+          <t>5,5; 15,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 19,53</t>
+          <t>8,1; 18,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 40,45</t>
+          <t>4,78; 40,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,48; 34,93</t>
+          <t>11,54; 34,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 29,24</t>
+          <t>7,35; 30,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,0; 28,8</t>
+          <t>13,82; 30,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,01; 18,97</t>
+          <t>6,17; 18,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,89; 19,01</t>
+          <t>8,27; 19,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 16,66</t>
+          <t>6,99; 16,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,8; 20,67</t>
+          <t>11,24; 20,64</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 12,48</t>
+          <t>5,73; 12,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,21; 26,87</t>
+          <t>15,56; 27,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 14,62</t>
+          <t>6,7; 14,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,32; 22,08</t>
+          <t>14,37; 22,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 15,63</t>
+          <t>3,73; 16,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,63; 34,55</t>
+          <t>12,75; 34,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,75; 32,32</t>
+          <t>12,98; 32,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 18,24</t>
+          <t>13,23; 22,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 12,28</t>
+          <t>6,25; 11,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,49; 26,98</t>
+          <t>16,78; 26,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,83; 17,9</t>
+          <t>9,71; 17,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 18,58</t>
+          <t>14,34; 20,59</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,54; 25,84</t>
+          <t>6,49; 23,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,22; 24,12</t>
+          <t>9,27; 24,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,18; 26,29</t>
+          <t>13,59; 26,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,68; 20,64</t>
+          <t>8,51; 18,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,86; 29,76</t>
+          <t>11,37; 28,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,23; 41,39</t>
+          <t>27,08; 41,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,97; 30,52</t>
+          <t>15,09; 29,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>24,52; 32,65</t>
+          <t>24,86; 33,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,93; 23,41</t>
+          <t>11,32; 24,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,6; 33,29</t>
+          <t>22,36; 33,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,43; 26,12</t>
+          <t>15,85; 25,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,75; 27,81</t>
+          <t>20,48; 27,41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,0</t>
+          <t>0,0; 71,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,9; 16,45</t>
+          <t>9,8; 16,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,03; 29,07</t>
+          <t>20,44; 29,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,88; 28,22</t>
+          <t>19,0; 28,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,11; 30,4</t>
+          <t>23,04; 30,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,46; 16,64</t>
+          <t>9,93; 16,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,03; 28,44</t>
+          <t>20,31; 29,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,88; 28,22</t>
+          <t>19,0; 28,5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,12; 30,15</t>
+          <t>23,42; 30,67</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,94; 10,42</t>
+          <t>6,04; 10,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,66; 18,09</t>
+          <t>11,98; 18,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,47 +1572,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,11; 15,19</t>
+          <t>10,53; 14,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,84; 16,11</t>
+          <t>11,15; 16,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,67; 29,04</t>
+          <t>22,35; 29,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,69; 25,34</t>
+          <t>18,39; 25,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,26; 23,49</t>
+          <t>21,02; 25,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,5; 13,16</t>
+          <t>9,39; 13,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,88; 23,78</t>
+          <t>18,88; 23,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,44; 19,78</t>
+          <t>15,5; 19,75</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,97; 19,08</t>
+          <t>16,86; 19,88</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10949</t>
+          <t>11517</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>819; 8645</t>
+          <t>794; 8465</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 10781</t>
+          <t>0; 10967</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>769; 10485</t>
+          <t>751; 9210</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3153; 10406</t>
+          <t>3052; 10135</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7232</t>
+          <t>0; 6552</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6777</t>
+          <t>0; 6751</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 8084</t>
+          <t>0; 8504</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2303; 8723</t>
+          <t>2623; 9816</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1712; 11430</t>
+          <t>1928; 11966</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1088; 12892</t>
+          <t>1123; 13414</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2155; 12617</t>
+          <t>1991; 13127</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6863; 16316</t>
+          <t>7462; 17515</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>13959</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3501</t>
+          <t>0; 4618</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1921; 13243</t>
+          <t>1241; 14297</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3476; 12984</t>
+          <t>3498; 12914</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3259; 12557</t>
+          <t>3592; 13071</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>906; 7293</t>
+          <t>907; 7731</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1029; 7360</t>
+          <t>1006; 8018</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1285; 10682</t>
+          <t>1342; 10075</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3167; 9754</t>
+          <t>3726; 11139</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1119; 9461</t>
+          <t>1177; 9112</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3503; 17229</t>
+          <t>4146; 17962</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6532; 20667</t>
+          <t>6414; 20010</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8325; 19526</t>
+          <t>9287; 21665</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>14259</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24069</t>
+          <t>26292</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2599; 11865</t>
+          <t>2612; 11732</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5073; 18822</t>
+          <t>5246; 19154</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6317; 17773</t>
+          <t>6616; 18276</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8881; 19929</t>
+          <t>9110; 20541</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1146; 9818</t>
+          <t>1161; 9783</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6269; 19079</t>
+          <t>6305; 19110</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2627; 13510</t>
+          <t>3395; 13869</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6864; 15201</t>
+          <t>8012; 17469</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5768; 18219</t>
+          <t>5929; 17945</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13663; 32938</t>
+          <t>14328; 33084</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11692; 27728</t>
+          <t>11629; 27325</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18278; 32007</t>
+          <t>19155; 35179</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>45299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>22335</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62596</t>
+          <t>67634</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14908; 32456</t>
+          <t>14906; 32545</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35259; 62267</t>
+          <t>36067; 64097</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13660; 29804</t>
+          <t>13659; 29919</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33837; 52175</t>
+          <t>37051; 57229</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3091; 13405</t>
+          <t>3194; 14412</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8190; 20763</t>
+          <t>7661; 20965</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12631; 32014</t>
+          <t>12859; 32140</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4826; 59499</t>
+          <t>17230; 28968</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20998; 42468</t>
+          <t>21612; 40819</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48119; 78742</t>
+          <t>48958; 77782</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29781; 54220</t>
+          <t>29427; 54347</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24143; 104488</t>
+          <t>55668; 79929</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>58103</t>
+          <t>63168</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71228</t>
+          <t>76544</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3625; 14334</t>
+          <t>3599; 13282</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9467; 24772</t>
+          <t>9519; 24721</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19141; 38179</t>
+          <t>19733; 38202</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8908; 18986</t>
+          <t>8580; 18928</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11415; 28647</t>
+          <t>10939; 27316</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51296; 77971</t>
+          <t>51013; 78328</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25484; 48693</t>
+          <t>24068; 47508</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49845; 66374</t>
+          <t>54239; 72884</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16586; 35522</t>
+          <t>17174; 36685</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65797; 96909</t>
+          <t>65075; 97362</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50078; 79596</t>
+          <t>48299; 78645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61275; 82117</t>
+          <t>65321; 87432</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>84354</t>
+          <t>92189</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85446</t>
+          <t>93370</t>
         </is>
       </c>
     </row>
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2275</t>
+          <t>0; 2348</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>42085; 69927</t>
+          <t>41652; 70601</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>79062; 114756</t>
+          <t>80658; 115643</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77971; 116582</t>
+          <t>78506; 117709</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>73745; 96987</t>
+          <t>79093; 105338</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40545; 71356</t>
+          <t>42578; 72265</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>79475; 112808</t>
+          <t>80583; 116028</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>77971; 116582</t>
+          <t>78506; 117709</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>74514; 97153</t>
+          <t>81157; 106317</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>82814</t>
+          <t>87410</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>184224</t>
+          <t>201905</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>267038</t>
+          <t>289315</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>29768; 52277</t>
+          <t>30304; 53159</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>65275; 101241</t>
+          <t>67035; 102984</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56165; 86052</t>
+          <t>56185; 86038</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70676; 96669</t>
+          <t>73654; 103991</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>73382; 109071</t>
+          <t>75498; 111199</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>168229; 215483</t>
+          <t>165839; 217038</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>144350; 195689</t>
+          <t>142024; 195290</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>93815; 237972</t>
+          <t>184869; 221175</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>111958; 155046</t>
+          <t>110613; 153564</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>245762; 309472</t>
+          <t>245775; 308054</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>210555; 269768</t>
+          <t>211340; 269386</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>164455; 314725</t>
+          <t>266159; 313798</t>
         </is>
       </c>
     </row>
